--- a/processo_im/1_Processo_Extracao_Dados/Comece_aqui/Planilha_Final/Planilha_GN_Atualizada.xlsx
+++ b/processo_im/1_Processo_Extracao_Dados/Comece_aqui/Planilha_Final/Planilha_GN_Atualizada.xlsx
@@ -568,28 +568,28 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Arquivo atualizado em: 2026-10-19 15:36:50</t>
+          <t>Arquivo atualizado em: 2026-10-20 00:18:46</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Atualizado por: Claude-teste-completo</t>
+          <t>Atualizado por: Flavio</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Computador: NCESD2-00310</t>
+          <t>Computador: SERVERWINDOWS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Início da execução: 2026-10-19 15:34:17</t>
+          <t>Início da execução: 2026-10-20 00:16:01</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -8770,7 +8770,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Claude-teste-completo</t>
+          <t>Flavio</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -8791,7 +8791,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NCESD2-00310</t>
+          <t>SERVERWINDOWS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -8812,7 +8812,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-19 15:34:17</t>
+          <t>2026-10-20 00:16:01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Sp_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Sp_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -8873,7 +8873,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Rj_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Rj_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Esgas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Esgas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Gasmig_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Gasmig_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Scgas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Scgas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Sulgas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Sulgas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Msgas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Msgas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Mtgas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Mtgas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Cigas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Cigas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Algas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Algas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Bahiagas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Bahiagas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Cegas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Cegas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Pbgas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Pbgas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -9302,7 +9302,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Copergas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Copergas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Potigas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Potigas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Sergipegas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Sergipegas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -9397,7 +9397,7 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Sp_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Sp_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -9430,7 +9430,7 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Rj_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Rj_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -9463,7 +9463,7 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Esgas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Esgas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -9496,7 +9496,7 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Gasmig_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Gasmig_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -9529,7 +9529,7 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -9562,7 +9562,7 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -9595,7 +9595,7 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -9628,7 +9628,7 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -9661,7 +9661,7 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -9694,7 +9694,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -9727,7 +9727,7 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -9760,7 +9760,7 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -9793,7 +9793,7 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -9826,7 +9826,7 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -9859,7 +9859,7 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -9892,7 +9892,7 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -9925,7 +9925,7 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -9958,7 +9958,7 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -9991,7 +9991,7 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Compagas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -10024,7 +10024,7 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Scgas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Scgas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -10057,7 +10057,7 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Sulgas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Sulgas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -10090,7 +10090,7 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Msgas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Msgas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -10123,7 +10123,7 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Mtgas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Mtgas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -10156,7 +10156,7 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Cigas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Cigas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -10189,7 +10189,7 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Algas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Algas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -10222,7 +10222,7 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Bahiagas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Bahiagas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -10255,7 +10255,7 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Cegas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Cegas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -10288,7 +10288,7 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Pbgas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Pbgas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -10321,7 +10321,7 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Copergas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Copergas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -10354,7 +10354,7 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Potigas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Potigas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10387,7 +10387,7 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>D:\DEV\IA%20-%20Calculadora%20GN\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Sergipegas_2026-10-19.xlsx</t>
+          <t>D:\Git\Copa\IA - Calculadora GN\6_Calculadora_Flask\processo_im\1_Processo_Extracao_Dados\Comece_aqui\Fonte_Dados\PlanilhasUf\Sergipegas_2026-10-20.xlsx</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
